--- a/backend/data/uploads/MES/2026-07-02_불량현황.xlsx
+++ b/backend/data/uploads/MES/2026-07-02_불량현황.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sihoo\PythonProject\TestProject\backend\data\uploads\MES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{51159D0A-FA9A-4A87-9B12-9206A3544610}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6B80E114-1A74-41FA-BA67-9E9081E42C50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{1B96AC32-4BDB-44A3-9969-90647743E50D}"/>
+    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{428C4FFE-ECA8-4C33-BCD9-DF7454CC6A55}"/>
   </bookViews>
   <sheets>
     <sheet name="불량현황" sheetId="1" r:id="rId1"/>
@@ -492,7 +492,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86CDDF6B-A908-4510-985D-D6BAD234D52D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FE3D2B1-E85E-4E74-9E81-63494DDA9869}">
   <dimension ref="B2:U12"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>

--- a/backend/data/uploads/MES/2026-07-02_불량현황.xlsx
+++ b/backend/data/uploads/MES/2026-07-02_불량현황.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sihoo\PythonProject\TestProject\backend\data\uploads\MES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6B80E114-1A74-41FA-BA67-9E9081E42C50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0F4AC9AE-EB48-47DF-8AA3-01F1788B72DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{428C4FFE-ECA8-4C33-BCD9-DF7454CC6A55}"/>
+    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{AFE107FC-1468-4DCD-B272-BD9FFDE04158}"/>
   </bookViews>
   <sheets>
     <sheet name="불량현황" sheetId="1" r:id="rId1"/>
@@ -492,7 +492,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FE3D2B1-E85E-4E74-9E81-63494DDA9869}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A83CEB3D-49C7-4A1C-A4D6-0E6302AD1E6A}">
   <dimension ref="B2:U12"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>

--- a/backend/data/uploads/MES/2026-07-02_불량현황.xlsx
+++ b/backend/data/uploads/MES/2026-07-02_불량현황.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sihoo\PythonProject\TestProject\backend\data\uploads\MES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0F4AC9AE-EB48-47DF-8AA3-01F1788B72DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{12A1C800-6798-47A2-B850-27F78474AEB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{AFE107FC-1468-4DCD-B272-BD9FFDE04158}"/>
+    <workbookView xWindow="-30240" yWindow="8376" windowWidth="23040" windowHeight="12012" xr2:uid="{82BD8E18-431D-4ED0-A569-7C10E0DD6341}"/>
   </bookViews>
   <sheets>
     <sheet name="불량현황" sheetId="1" r:id="rId1"/>
@@ -492,7 +492,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A83CEB3D-49C7-4A1C-A4D6-0E6302AD1E6A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE703514-8881-4D6C-B43C-21C7C8123AC0}">
   <dimension ref="B2:U12"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
